--- a/docs/obsoletos/Cronograma Físico Financeiro WAVE - FIP rev 07 percentuais.xlsx
+++ b/docs/obsoletos/Cronograma Físico Financeiro WAVE - FIP rev 07 percentuais.xlsx
@@ -5,10 +5,10 @@
   <workbookPr codeName="EstaPastaDeTrabalho"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/b73f7ac4adb68b79/APP-GESTAO-CONTRATO/docs/"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/b73f7ac4adb68b79/APP-GESTAO-CONTRATO/docs/obsoletos/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="600" documentId="8_{66E8BC8A-DCAE-49C6-B59C-AFC9CA3C8614}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{34BDF1B8-5E57-4F58-82B1-660DF41AC7C2}"/>
+  <xr:revisionPtr revIDLastSave="625" documentId="8_{66E8BC8A-DCAE-49C6-B59C-AFC9CA3C8614}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{E41D47A3-358E-4716-91FD-5F213FDEC4D2}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" tabRatio="601" xr2:uid="{37B66749-6C7B-43A5-9069-298DC434CDF1}"/>
   </bookViews>
@@ -2679,7 +2679,7 @@
     <numFmt numFmtId="165" formatCode="_-&quot;R$&quot;\ * #,##0.000_-;\-&quot;R$&quot;\ * #,##0.000_-;_-&quot;R$&quot;\ * &quot;-&quot;??_-;_-@_-"/>
     <numFmt numFmtId="166" formatCode="0.0%"/>
   </numFmts>
-  <fonts count="20" x14ac:knownFonts="1">
+  <fonts count="21" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -2837,6 +2837,11 @@
       <name val="Segoe UI"/>
       <family val="2"/>
     </font>
+    <font>
+      <sz val="10"/>
+      <color rgb="FF000000"/>
+      <name val="Calibri"/>
+    </font>
   </fonts>
   <fills count="10">
     <fill>
@@ -2894,7 +2899,7 @@
       </patternFill>
     </fill>
   </fills>
-  <borders count="9">
+  <borders count="10">
     <border>
       <left/>
       <right/>
@@ -3000,13 +3005,28 @@
       </bottom>
       <diagonal/>
     </border>
+    <border>
+      <left style="thin">
+        <color rgb="FFB0B0B0"/>
+      </left>
+      <right style="thin">
+        <color rgb="FFB0B0B0"/>
+      </right>
+      <top style="thin">
+        <color rgb="FFB0B0B0"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="FFB0B0B0"/>
+      </bottom>
+      <diagonal/>
+    </border>
   </borders>
   <cellStyleXfs count="3">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="44" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
     <xf numFmtId="9" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="85">
+  <cellXfs count="86">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
@@ -3246,6 +3266,9 @@
     <xf numFmtId="9" fontId="3" fillId="9" borderId="1" xfId="2" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
+    <xf numFmtId="44" fontId="20" fillId="0" borderId="9" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
     <xf numFmtId="44" fontId="2" fillId="6" borderId="7" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
@@ -3294,7 +3317,238 @@
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
     <cellStyle name="Porcentagem" xfId="2" builtinId="5"/>
   </cellStyles>
-  <dxfs count="24">
+  <dxfs count="57">
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor theme="7" tint="0.59996337778862885"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor theme="7" tint="0.59996337778862885"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor theme="7" tint="0.59996337778862885"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor theme="7" tint="0.59996337778862885"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor theme="7" tint="0.59996337778862885"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor theme="7" tint="0.59996337778862885"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor theme="7" tint="0.59996337778862885"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor theme="7" tint="0.59996337778862885"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor theme="7" tint="0.59996337778862885"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor theme="7" tint="0.59996337778862885"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor theme="7" tint="0.59996337778862885"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor theme="7" tint="0.59996337778862885"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor theme="7" tint="0.59996337778862885"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor theme="7" tint="0.59996337778862885"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor theme="7" tint="0.59996337778862885"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor theme="7" tint="0.59996337778862885"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor theme="7" tint="0.59996337778862885"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor theme="7" tint="0.59996337778862885"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor theme="7" tint="0.59996337778862885"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor theme="7" tint="0.59996337778862885"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor theme="7" tint="0.59996337778862885"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor theme="7" tint="0.59996337778862885"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor theme="7" tint="0.59996337778862885"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor theme="7" tint="0.59996337778862885"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor theme="7" tint="0.59996337778862885"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor theme="7" tint="0.59996337778862885"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor theme="7" tint="0.59996337778862885"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor theme="7" tint="0.59996337778862885"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor theme="7" tint="0.59996337778862885"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor theme="7" tint="0.59996337778862885"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor theme="7" tint="0.59996337778862885"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor theme="7" tint="0.59996337778862885"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor theme="7" tint="0.59996337778862885"/>
+        </patternFill>
+      </fill>
+    </dxf>
     <dxf>
       <font>
         <color theme="0"/>
@@ -3480,10 +3734,6 @@
     </ext>
   </extLst>
 </styleSheet>
-</file>
-
-<file path=xl/persons/person.xml><?xml version="1.0" encoding="utf-8"?>
-<personList xmlns="http://schemas.microsoft.com/office/spreadsheetml/2018/threadedcomments" xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main"/>
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
@@ -3803,11 +4053,11 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{21612B2B-65B0-4042-AF89-F6179AF39AA4}">
-  <sheetPr codeName="Planilha1" filterMode="1">
+  <sheetPr codeName="Planilha1">
     <outlinePr summaryBelow="0"/>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="B1:BB413"/>
+  <dimension ref="B1:BB410"/>
   <sheetFormatPr defaultColWidth="8.6640625" defaultRowHeight="12" outlineLevelRow="2" outlineLevelCol="1" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="2.44140625" style="36" customWidth="1"/>
@@ -3820,28 +4070,28 @@
     <col min="8" max="8" width="16.88671875" style="37" bestFit="1" customWidth="1"/>
     <col min="9" max="9" width="16.44140625" style="37" bestFit="1" customWidth="1"/>
     <col min="10" max="10" width="16.88671875" style="37" bestFit="1" customWidth="1"/>
-    <col min="11" max="11" width="5.88671875" style="36" hidden="1" customWidth="1" outlineLevel="1"/>
-    <col min="12" max="12" width="10.33203125" style="38" hidden="1" customWidth="1" outlineLevel="1"/>
-    <col min="13" max="13" width="9.6640625" style="38" hidden="1" customWidth="1" outlineLevel="1"/>
-    <col min="14" max="14" width="11.5546875" style="38" hidden="1" customWidth="1" outlineLevel="1"/>
-    <col min="15" max="15" width="9.6640625" style="38" hidden="1" customWidth="1" outlineLevel="1"/>
-    <col min="16" max="16" width="9.33203125" style="38" hidden="1" customWidth="1" outlineLevel="1"/>
-    <col min="17" max="17" width="10.109375" style="38" hidden="1" customWidth="1" outlineLevel="1"/>
-    <col min="18" max="18" width="9.6640625" style="38" hidden="1" customWidth="1" outlineLevel="1"/>
-    <col min="19" max="19" width="10" style="38" hidden="1" customWidth="1" outlineLevel="1"/>
-    <col min="20" max="20" width="10.33203125" style="38" hidden="1" customWidth="1" outlineLevel="1"/>
-    <col min="21" max="21" width="10.109375" style="38" hidden="1" customWidth="1" outlineLevel="1"/>
-    <col min="22" max="23" width="9.6640625" style="38" hidden="1" customWidth="1" outlineLevel="1"/>
-    <col min="24" max="24" width="10.33203125" style="38" hidden="1" customWidth="1" outlineLevel="1"/>
-    <col min="25" max="25" width="9.6640625" style="38" hidden="1" customWidth="1" outlineLevel="1"/>
-    <col min="26" max="26" width="10.109375" style="38" hidden="1" customWidth="1" outlineLevel="1"/>
-    <col min="27" max="27" width="9.6640625" style="38" hidden="1" customWidth="1" outlineLevel="1"/>
-    <col min="28" max="28" width="9.33203125" style="38" hidden="1" customWidth="1" outlineLevel="1"/>
-    <col min="29" max="29" width="10.109375" style="38" hidden="1" customWidth="1" outlineLevel="1"/>
-    <col min="30" max="30" width="9.6640625" style="38" hidden="1" customWidth="1" outlineLevel="1"/>
-    <col min="31" max="31" width="10" style="38" hidden="1" customWidth="1" outlineLevel="1"/>
-    <col min="32" max="32" width="12.6640625" style="36" hidden="1" customWidth="1" outlineLevel="1"/>
-    <col min="33" max="33" width="1.6640625" style="36" customWidth="1" collapsed="1"/>
+    <col min="11" max="11" width="5.88671875" style="36" customWidth="1" outlineLevel="1"/>
+    <col min="12" max="12" width="10.33203125" style="38" customWidth="1" outlineLevel="1"/>
+    <col min="13" max="13" width="9.6640625" style="38" customWidth="1" outlineLevel="1"/>
+    <col min="14" max="14" width="11.5546875" style="38" customWidth="1" outlineLevel="1"/>
+    <col min="15" max="15" width="9.6640625" style="38" customWidth="1" outlineLevel="1"/>
+    <col min="16" max="16" width="9.33203125" style="38" customWidth="1" outlineLevel="1"/>
+    <col min="17" max="17" width="10.109375" style="38" customWidth="1" outlineLevel="1"/>
+    <col min="18" max="18" width="9.6640625" style="38" customWidth="1" outlineLevel="1"/>
+    <col min="19" max="19" width="10" style="38" customWidth="1" outlineLevel="1"/>
+    <col min="20" max="20" width="10.33203125" style="38" customWidth="1" outlineLevel="1"/>
+    <col min="21" max="21" width="10.109375" style="38" customWidth="1" outlineLevel="1"/>
+    <col min="22" max="23" width="9.6640625" style="38" customWidth="1" outlineLevel="1"/>
+    <col min="24" max="24" width="10.33203125" style="38" customWidth="1" outlineLevel="1"/>
+    <col min="25" max="25" width="9.6640625" style="38" customWidth="1" outlineLevel="1"/>
+    <col min="26" max="26" width="10.109375" style="38" customWidth="1" outlineLevel="1"/>
+    <col min="27" max="27" width="9.6640625" style="38" customWidth="1" outlineLevel="1"/>
+    <col min="28" max="28" width="9.33203125" style="38" customWidth="1" outlineLevel="1"/>
+    <col min="29" max="29" width="10.109375" style="38" customWidth="1" outlineLevel="1"/>
+    <col min="30" max="30" width="9.6640625" style="38" customWidth="1" outlineLevel="1"/>
+    <col min="31" max="31" width="10" style="38" customWidth="1" outlineLevel="1"/>
+    <col min="32" max="32" width="12.6640625" style="36" customWidth="1" outlineLevel="1"/>
+    <col min="33" max="33" width="1.6640625" style="36" customWidth="1"/>
     <col min="34" max="34" width="11.33203125" style="38" hidden="1" customWidth="1"/>
     <col min="35" max="53" width="11.33203125" style="38" customWidth="1"/>
     <col min="54" max="54" width="12.6640625" style="36" bestFit="1" customWidth="1"/>
@@ -3956,90 +4206,90 @@
       </c>
     </row>
     <row r="2" spans="2:54" s="1" customFormat="1" ht="14.4" x14ac:dyDescent="0.3">
-      <c r="B2" s="73" t="s">
+      <c r="B2" s="74" t="s">
         <v>63</v>
       </c>
-      <c r="C2" s="80" t="s">
-        <v>0</v>
-      </c>
-      <c r="D2" s="73" t="s">
+      <c r="C2" s="81" t="s">
+        <v>0</v>
+      </c>
+      <c r="D2" s="74" t="s">
         <v>92</v>
       </c>
-      <c r="E2" s="83" t="s">
+      <c r="E2" s="84" t="s">
         <v>800</v>
       </c>
-      <c r="F2" s="80" t="s">
-        <v>1</v>
-      </c>
-      <c r="G2" s="80" t="s">
+      <c r="F2" s="81" t="s">
+        <v>1</v>
+      </c>
+      <c r="G2" s="81" t="s">
         <v>90</v>
       </c>
-      <c r="H2" s="76" t="s">
+      <c r="H2" s="77" t="s">
         <v>61</v>
       </c>
-      <c r="I2" s="76" t="s">
+      <c r="I2" s="77" t="s">
         <v>62</v>
       </c>
-      <c r="J2" s="76" t="s">
+      <c r="J2" s="77" t="s">
         <v>137</v>
       </c>
-      <c r="L2" s="78" t="s">
+      <c r="L2" s="79" t="s">
         <v>2</v>
       </c>
-      <c r="M2" s="78"/>
-      <c r="N2" s="78"/>
-      <c r="O2" s="78"/>
-      <c r="P2" s="78"/>
-      <c r="Q2" s="78"/>
-      <c r="R2" s="78"/>
-      <c r="S2" s="78"/>
-      <c r="T2" s="78"/>
-      <c r="U2" s="78"/>
-      <c r="V2" s="78"/>
-      <c r="W2" s="78"/>
-      <c r="X2" s="78"/>
-      <c r="Y2" s="78"/>
-      <c r="Z2" s="78"/>
-      <c r="AA2" s="78"/>
-      <c r="AB2" s="78"/>
-      <c r="AC2" s="78"/>
-      <c r="AD2" s="78"/>
-      <c r="AE2" s="78"/>
-      <c r="AF2" s="79"/>
-      <c r="AH2" s="71" t="s">
+      <c r="M2" s="79"/>
+      <c r="N2" s="79"/>
+      <c r="O2" s="79"/>
+      <c r="P2" s="79"/>
+      <c r="Q2" s="79"/>
+      <c r="R2" s="79"/>
+      <c r="S2" s="79"/>
+      <c r="T2" s="79"/>
+      <c r="U2" s="79"/>
+      <c r="V2" s="79"/>
+      <c r="W2" s="79"/>
+      <c r="X2" s="79"/>
+      <c r="Y2" s="79"/>
+      <c r="Z2" s="79"/>
+      <c r="AA2" s="79"/>
+      <c r="AB2" s="79"/>
+      <c r="AC2" s="79"/>
+      <c r="AD2" s="79"/>
+      <c r="AE2" s="79"/>
+      <c r="AF2" s="80"/>
+      <c r="AH2" s="72" t="s">
         <v>809</v>
       </c>
-      <c r="AI2" s="71"/>
-      <c r="AJ2" s="71"/>
-      <c r="AK2" s="71"/>
-      <c r="AL2" s="71"/>
-      <c r="AM2" s="71"/>
-      <c r="AN2" s="71"/>
-      <c r="AO2" s="71"/>
-      <c r="AP2" s="71"/>
-      <c r="AQ2" s="71"/>
-      <c r="AR2" s="71"/>
-      <c r="AS2" s="71"/>
-      <c r="AT2" s="71"/>
-      <c r="AU2" s="71"/>
-      <c r="AV2" s="71"/>
-      <c r="AW2" s="71"/>
-      <c r="AX2" s="71"/>
-      <c r="AY2" s="71"/>
-      <c r="AZ2" s="71"/>
-      <c r="BA2" s="71"/>
-      <c r="BB2" s="72"/>
+      <c r="AI2" s="72"/>
+      <c r="AJ2" s="72"/>
+      <c r="AK2" s="72"/>
+      <c r="AL2" s="72"/>
+      <c r="AM2" s="72"/>
+      <c r="AN2" s="72"/>
+      <c r="AO2" s="72"/>
+      <c r="AP2" s="72"/>
+      <c r="AQ2" s="72"/>
+      <c r="AR2" s="72"/>
+      <c r="AS2" s="72"/>
+      <c r="AT2" s="72"/>
+      <c r="AU2" s="72"/>
+      <c r="AV2" s="72"/>
+      <c r="AW2" s="72"/>
+      <c r="AX2" s="72"/>
+      <c r="AY2" s="72"/>
+      <c r="AZ2" s="72"/>
+      <c r="BA2" s="72"/>
+      <c r="BB2" s="73"/>
     </row>
     <row r="3" spans="2:54" s="1" customFormat="1" ht="14.4" x14ac:dyDescent="0.3">
-      <c r="B3" s="74"/>
-      <c r="C3" s="81"/>
-      <c r="D3" s="74"/>
-      <c r="E3" s="84"/>
-      <c r="F3" s="81"/>
-      <c r="G3" s="81"/>
-      <c r="H3" s="77"/>
-      <c r="I3" s="77"/>
-      <c r="J3" s="77"/>
+      <c r="B3" s="75"/>
+      <c r="C3" s="82"/>
+      <c r="D3" s="75"/>
+      <c r="E3" s="85"/>
+      <c r="F3" s="82"/>
+      <c r="G3" s="82"/>
+      <c r="H3" s="78"/>
+      <c r="I3" s="78"/>
+      <c r="J3" s="78"/>
       <c r="L3" s="3">
         <v>46111</v>
       </c>
@@ -4167,88 +4417,88 @@
         <v>136</v>
       </c>
     </row>
-    <row r="4" spans="2:54" s="1" customFormat="1" ht="14.4" hidden="1" x14ac:dyDescent="0.3">
-      <c r="B4" s="74"/>
-      <c r="C4" s="81"/>
-      <c r="D4" s="74"/>
+    <row r="4" spans="2:54" s="1" customFormat="1" ht="14.4" x14ac:dyDescent="0.3">
+      <c r="B4" s="75"/>
+      <c r="C4" s="82"/>
+      <c r="D4" s="75"/>
       <c r="E4" s="67"/>
-      <c r="F4" s="81"/>
-      <c r="G4" s="81"/>
-      <c r="H4" s="76">
+      <c r="F4" s="82"/>
+      <c r="G4" s="82"/>
+      <c r="H4" s="77">
         <f>H6+H35+H54+H86+H134+H151+H167+H181+H202+H220+H252+H257+H267+H296+H328+H376+H391+H407</f>
         <v>11300000.001659999</v>
       </c>
-      <c r="I4" s="76">
+      <c r="I4" s="77">
         <f>I6+I35+I54+I86+I134+I151+I167+I181+I202+I220+I252+I257+I267+I296+I328+I376+I391+I407</f>
         <v>6699999.9991725115</v>
       </c>
-      <c r="J4" s="76">
+      <c r="J4" s="77">
         <f>J6+J35+J54+J86+J134+J151+J167+J181+J202+J220+J252+J257+J267+J296+J328+J376+J391+J407</f>
         <v>18000000.000832513</v>
       </c>
       <c r="L4" s="5">
         <f t="shared" ref="L4:AE4" si="0">SUMPRODUCT(L6:L411,$J6:$J411)/$J$4/3</f>
-        <v>3.0084855762497454E-3</v>
+        <v>0</v>
       </c>
       <c r="M4" s="5">
         <f t="shared" si="0"/>
-        <v>1.2839853263295039E-3</v>
+        <v>4.2924853859125497E-3</v>
       </c>
       <c r="N4" s="5">
         <f t="shared" si="0"/>
-        <v>3.8434671030755048E-2</v>
+        <v>3.8434678272421703E-2</v>
       </c>
       <c r="O4" s="5">
         <f t="shared" si="0"/>
-        <v>5.2701230679677975E-2</v>
+        <v>5.2701237921344631E-2</v>
       </c>
       <c r="P4" s="5">
         <f t="shared" si="0"/>
-        <v>7.1239900880566781E-2</v>
+        <v>7.1239908122233436E-2</v>
       </c>
       <c r="Q4" s="5">
         <f t="shared" si="0"/>
-        <v>0.19594595001358159</v>
+        <v>0.1959459572552483</v>
       </c>
       <c r="R4" s="5">
         <f t="shared" si="0"/>
-        <v>0.10610082012378008</v>
+        <v>0.10610082736544675</v>
       </c>
       <c r="S4" s="5">
         <f t="shared" si="0"/>
-        <v>6.37462500861046E-2</v>
+        <v>6.3746257327771255E-2</v>
       </c>
       <c r="T4" s="5">
         <f t="shared" si="0"/>
-        <v>6.0131491590951547E-2</v>
+        <v>6.0131498832618202E-2</v>
       </c>
       <c r="U4" s="5">
         <f t="shared" si="0"/>
-        <v>5.106398997610484E-2</v>
+        <v>5.1063997217771495E-2</v>
       </c>
       <c r="V4" s="5">
         <f t="shared" si="0"/>
-        <v>4.5891196167568489E-2</v>
+        <v>4.5891203409235144E-2</v>
       </c>
       <c r="W4" s="5">
         <f t="shared" si="0"/>
-        <v>3.9571996974902594E-2</v>
+        <v>3.957200421656925E-2</v>
       </c>
       <c r="X4" s="5">
         <f t="shared" si="0"/>
-        <v>3.9804733952169609E-2</v>
+        <v>3.9804741193836264E-2</v>
       </c>
       <c r="Y4" s="5">
         <f t="shared" si="0"/>
-        <v>3.6254847154556007E-2</v>
+        <v>3.6254854396222662E-2</v>
       </c>
       <c r="Z4" s="5">
         <f t="shared" si="0"/>
-        <v>4.8519953743070221E-2</v>
+        <v>4.8519960984736876E-2</v>
       </c>
       <c r="AA4" s="5">
         <f t="shared" si="0"/>
-        <v>5.696557563774917E-2</v>
+        <v>5.6965582879415826E-2</v>
       </c>
       <c r="AB4" s="5">
         <f t="shared" si="0"/>
@@ -4268,7 +4518,7 @@
       </c>
       <c r="AF4" s="6">
         <f>SUM(M4:AE4)</f>
-        <v>0.99697369907638966</v>
+        <v>0.99998230051930592</v>
       </c>
       <c r="AH4" s="48">
         <f t="shared" ref="AH4:BA4" si="1">(AH6*$H6+AH35*$H35+AH54*$H54+AH86*$H86+AH134*$H134+AH151*$H151+AH167*$H167+AH181*$H181+AH202*$H202+AH220*$H220+AH252*$H252+AH257*$H257+AH267*$H267+AH296*$H296+AH328*$H328+AH376*$H376+AH391*$H391+AH407*$H407)/$H$4</f>
@@ -4276,7 +4526,7 @@
       </c>
       <c r="AI4" s="48">
         <f t="shared" si="1"/>
-        <v>0.16125762870275323</v>
+        <v>0.16125769186552733</v>
       </c>
       <c r="AJ4" s="48">
         <f t="shared" si="1"/>
@@ -4312,7 +4562,7 @@
       </c>
       <c r="AR4" s="48">
         <f t="shared" si="1"/>
-        <v>1.1227524963346214E-2</v>
+        <v>1.1227567071862286E-2</v>
       </c>
       <c r="AS4" s="48">
         <f t="shared" si="1"/>
@@ -4352,100 +4602,100 @@
       </c>
       <c r="BB4" s="49">
         <f>SUM(AH4:BA4)</f>
-        <v>1.0000000000000002</v>
+        <v>1.0000001052712904</v>
       </c>
     </row>
-    <row r="5" spans="2:54" s="1" customFormat="1" ht="14.4" hidden="1" x14ac:dyDescent="0.3">
-      <c r="B5" s="75"/>
-      <c r="C5" s="82"/>
-      <c r="D5" s="75"/>
+    <row r="5" spans="2:54" s="1" customFormat="1" ht="14.4" x14ac:dyDescent="0.3">
+      <c r="B5" s="76"/>
+      <c r="C5" s="83"/>
+      <c r="D5" s="76"/>
       <c r="E5" s="66" t="s">
         <v>810</v>
       </c>
-      <c r="F5" s="82"/>
-      <c r="G5" s="82"/>
-      <c r="H5" s="77"/>
-      <c r="I5" s="77"/>
-      <c r="J5" s="77"/>
+      <c r="F5" s="83"/>
+      <c r="G5" s="83"/>
+      <c r="H5" s="78"/>
+      <c r="I5" s="78"/>
+      <c r="J5" s="78"/>
       <c r="L5" s="5">
         <f>L4</f>
-        <v>3.0084855762497454E-3</v>
+        <v>0</v>
       </c>
       <c r="M5" s="5">
         <f>L5+M4</f>
-        <v>4.2924709025792488E-3</v>
+        <v>4.2924853859125497E-3</v>
       </c>
       <c r="N5" s="5">
         <f t="shared" ref="N5:AE5" si="2">M5+N4</f>
-        <v>4.2727141933334295E-2</v>
+        <v>4.2727163658334254E-2</v>
       </c>
       <c r="O5" s="5">
         <f t="shared" si="2"/>
-        <v>9.5428372613012263E-2</v>
+        <v>9.5428401579678884E-2</v>
       </c>
       <c r="P5" s="5">
         <f t="shared" si="2"/>
-        <v>0.16666827349357904</v>
+        <v>0.16666830970191232</v>
       </c>
       <c r="Q5" s="5">
         <f t="shared" si="2"/>
-        <v>0.36261422350716066</v>
+        <v>0.36261426695716059</v>
       </c>
       <c r="R5" s="5">
         <f t="shared" si="2"/>
-        <v>0.46871504363094074</v>
+        <v>0.46871509432260733</v>
       </c>
       <c r="S5" s="5">
         <f t="shared" si="2"/>
-        <v>0.53246129371704531</v>
+        <v>0.53246135165037856</v>
       </c>
       <c r="T5" s="5">
         <f t="shared" si="2"/>
-        <v>0.59259278530799686</v>
+        <v>0.5925928504829967</v>
       </c>
       <c r="U5" s="5">
         <f t="shared" si="2"/>
-        <v>0.6436567752841017</v>
+        <v>0.64365684770076825</v>
       </c>
       <c r="V5" s="5">
         <f t="shared" si="2"/>
-        <v>0.68954797145167024</v>
+        <v>0.68954805111000339</v>
       </c>
       <c r="W5" s="5">
         <f t="shared" si="2"/>
-        <v>0.72911996842657278</v>
+        <v>0.72912005532657265</v>
       </c>
       <c r="X5" s="5">
         <f t="shared" si="2"/>
-        <v>0.76892470237874244</v>
+        <v>0.7689247965204089</v>
       </c>
       <c r="Y5" s="5">
         <f t="shared" si="2"/>
-        <v>0.8051795495332984</v>
+        <v>0.80517965091663157</v>
       </c>
       <c r="Z5" s="5">
         <f t="shared" si="2"/>
-        <v>0.85369950327636857</v>
+        <v>0.85369961190136845</v>
       </c>
       <c r="AA5" s="5">
         <f t="shared" si="2"/>
-        <v>0.91066507891411774</v>
+        <v>0.91066519478078423</v>
       </c>
       <c r="AB5" s="5">
         <f t="shared" si="2"/>
-        <v>0.95653813878992977</v>
+        <v>0.95653825465659625</v>
       </c>
       <c r="AC5" s="5">
         <f t="shared" si="2"/>
-        <v>0.99173935682145475</v>
+        <v>0.99173947268812124</v>
       </c>
       <c r="AD5" s="5">
         <f t="shared" si="2"/>
-        <v>0.99990520163643193</v>
+        <v>0.99990531750309841</v>
       </c>
       <c r="AE5" s="5">
         <f t="shared" si="2"/>
-        <v>0.99998218465263944</v>
+        <v>0.99998230051930592</v>
       </c>
       <c r="AF5" s="6"/>
       <c r="AH5" s="48">
@@ -4454,79 +4704,79 @@
       </c>
       <c r="AI5" s="48">
         <f>AH5+AI4</f>
-        <v>0.16125762870275323</v>
+        <v>0.16125769186552733</v>
       </c>
       <c r="AJ5" s="48">
         <f t="shared" ref="AJ5:BA5" si="3">AI5+AJ4</f>
-        <v>0.25460510462169933</v>
+        <v>0.2546051677844734</v>
       </c>
       <c r="AK5" s="48">
         <f t="shared" si="3"/>
-        <v>0.33696374869454049</v>
+        <v>0.33696381185731455</v>
       </c>
       <c r="AL5" s="48">
         <f t="shared" si="3"/>
-        <v>0.56115974681008596</v>
+        <v>0.56115980997286008</v>
       </c>
       <c r="AM5" s="48">
         <f t="shared" si="3"/>
-        <v>0.61188539955279908</v>
+        <v>0.6118854627155732</v>
       </c>
       <c r="AN5" s="48">
         <f t="shared" si="3"/>
-        <v>0.63007929396047668</v>
+        <v>0.63007935712325081</v>
       </c>
       <c r="AO5" s="48">
         <f t="shared" si="3"/>
-        <v>0.64372177240808781</v>
+        <v>0.64372183557086193</v>
       </c>
       <c r="AP5" s="48">
         <f t="shared" si="3"/>
-        <v>0.73545393093301303</v>
+        <v>0.73545399409578716</v>
       </c>
       <c r="AQ5" s="48">
         <f t="shared" si="3"/>
-        <v>0.8487664402677022</v>
+        <v>0.84876650343047633</v>
       </c>
       <c r="AR5" s="48">
         <f t="shared" si="3"/>
-        <v>0.85999396523104843</v>
+        <v>0.85999407050233856</v>
       </c>
       <c r="AS5" s="48">
         <f t="shared" si="3"/>
-        <v>0.87463530185819227</v>
+        <v>0.8746354071294824</v>
       </c>
       <c r="AT5" s="48">
         <f t="shared" si="3"/>
-        <v>0.89254066740545324</v>
+        <v>0.89254077267674337</v>
       </c>
       <c r="AU5" s="48">
         <f t="shared" si="3"/>
-        <v>0.91908482674385694</v>
+        <v>0.91908493201514707</v>
       </c>
       <c r="AV5" s="48">
         <f t="shared" si="3"/>
-        <v>0.95022458833531886</v>
+        <v>0.95022469360660899</v>
       </c>
       <c r="AW5" s="48">
         <f t="shared" si="3"/>
-        <v>0.9617028550299872</v>
+        <v>0.96170296030127733</v>
       </c>
       <c r="AX5" s="48">
         <f t="shared" si="3"/>
-        <v>0.98614255526187833</v>
+        <v>0.98614266053316846</v>
       </c>
       <c r="AY5" s="48">
         <f t="shared" si="3"/>
-        <v>0.99644247787662898</v>
+        <v>0.99644258314791911</v>
       </c>
       <c r="AZ5" s="48">
         <f t="shared" si="3"/>
-        <v>1.0000000000000002</v>
+        <v>1.0000001052712904</v>
       </c>
       <c r="BA5" s="48">
         <f t="shared" si="3"/>
-        <v>1.0000000000000002</v>
+        <v>1.0000001052712904</v>
       </c>
       <c r="BB5" s="48"/>
     </row>
@@ -5276,7 +5526,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="11" spans="2:54" s="17" customFormat="1" ht="13.8" outlineLevel="1" x14ac:dyDescent="0.3">
+    <row r="11" spans="2:54" s="17" customFormat="1" ht="27.6" outlineLevel="1" x14ac:dyDescent="0.3">
       <c r="B11" s="11">
         <v>2</v>
       </c>
@@ -20670,7 +20920,7 @@
       </c>
       <c r="K151" s="21"/>
       <c r="L151" s="10" t="str">
-        <f t="shared" ref="L151:Q151" si="106">IF(L152=0,"",L152)</f>
+        <f t="shared" ref="L151:AA151" si="106">IF(L152=0,"",L152)</f>
         <v/>
       </c>
       <c r="M151" s="10" t="str">
@@ -27962,7 +28212,7 @@
         <v>0.99999999999999978</v>
       </c>
     </row>
-    <row r="222" spans="2:54" s="29" customFormat="1" outlineLevel="2" x14ac:dyDescent="0.3">
+    <row r="222" spans="2:54" s="29" customFormat="1" ht="24" outlineLevel="2" x14ac:dyDescent="0.3">
       <c r="B222" s="23">
         <v>3</v>
       </c>
@@ -45267,69 +45517,69 @@
         <f>J392</f>
         <v>335924.86</v>
       </c>
-      <c r="L391" s="10">
+      <c r="L391" s="10" t="str">
         <f t="shared" ref="L391:AE391" si="244">IF(L392=0,"",L392)</f>
-        <v>0.16120492057360689</v>
+        <v/>
       </c>
       <c r="M391" s="10">
         <f t="shared" si="244"/>
-        <v>6.8800314079166411E-2</v>
+        <v>0.23000601071918123</v>
       </c>
       <c r="N391" s="10">
         <f t="shared" si="244"/>
-        <v>6.8800314079166411E-2</v>
+        <v>6.8800702112370368E-2</v>
       </c>
       <c r="O391" s="10">
         <f t="shared" si="244"/>
-        <v>6.8800314079166411E-2</v>
+        <v>6.8800702112370368E-2</v>
       </c>
       <c r="P391" s="10">
         <f t="shared" si="244"/>
-        <v>6.8800314079166411E-2</v>
+        <v>6.8800702112370368E-2</v>
       </c>
       <c r="Q391" s="10">
         <f t="shared" si="244"/>
-        <v>6.8800314079166411E-2</v>
+        <v>6.8800702112370368E-2</v>
       </c>
       <c r="R391" s="10">
         <f t="shared" si="244"/>
-        <v>9.9973826736133795E-3</v>
+        <v>9.9977707068173421E-3</v>
       </c>
       <c r="S391" s="10">
         <f t="shared" si="244"/>
-        <v>6.8800314079166411E-2</v>
+        <v>6.8800702112370368E-2</v>
       </c>
       <c r="T391" s="10">
         <f t="shared" si="244"/>
-        <v>6.8800314079166411E-2</v>
+        <v>6.8800702112370368E-2</v>
       </c>
       <c r="U391" s="10">
         <f t="shared" si="244"/>
-        <v>6.8800314079166411E-2</v>
+        <v>6.8800702112370368E-2</v>
       </c>
       <c r="V391" s="10">
         <f t="shared" si="244"/>
-        <v>9.9973826736133795E-3</v>
+        <v>9.9977707068173421E-3</v>
       </c>
       <c r="W391" s="10">
         <f>IF(W392=0,"",W392)</f>
-        <v>6.8800314079166411E-2</v>
+        <v>6.8800702112370368E-2</v>
       </c>
       <c r="X391" s="10">
         <f t="shared" si="244"/>
-        <v>6.8800314079166411E-2</v>
+        <v>6.8800702112370368E-2</v>
       </c>
       <c r="Y391" s="10">
         <f t="shared" si="244"/>
-        <v>9.9973826736133795E-3</v>
+        <v>9.9977707068173421E-3</v>
       </c>
       <c r="Z391" s="10">
         <f t="shared" si="244"/>
-        <v>9.9973826736133795E-3</v>
+        <v>9.9977707068173421E-3</v>
       </c>
       <c r="AA391" s="10">
         <f>IF(AA392=0,"",AA392)</f>
-        <v>0.1108024079402757</v>
+        <v>0.11080279597347965</v>
       </c>
       <c r="AB391" s="10" t="str">
         <f>IF(AB392=0,"",AB392)</f>
@@ -45349,7 +45599,7 @@
       </c>
       <c r="AF391" s="6">
         <f>SUM(L391:AE391)</f>
-        <v>1.0000000000000002</v>
+        <v>1.0000062085312631</v>
       </c>
       <c r="AH391" s="10">
         <f t="shared" ref="AH391:BA391" si="245">IF(AH392=0,,AH392)</f>
@@ -45357,7 +45607,7 @@
       </c>
       <c r="AI391" s="10">
         <f t="shared" si="245"/>
-        <v>0.54119706859444705</v>
+        <v>0.54120079371320517</v>
       </c>
       <c r="AJ391" s="10">
         <f t="shared" si="245"/>
@@ -45393,7 +45643,7 @@
       </c>
       <c r="AR391" s="10">
         <f t="shared" si="245"/>
-        <v>0.28239413718889395</v>
+        <v>0.28239662060139936</v>
       </c>
       <c r="AS391" s="10">
         <f t="shared" si="245"/>
@@ -45433,7 +45683,7 @@
       </c>
       <c r="BB391" s="49">
         <f>SUM(AH391:BA391)</f>
-        <v>1</v>
+        <v>1.0000062085312638</v>
       </c>
     </row>
     <row r="392" spans="2:54" s="17" customFormat="1" ht="13.8" outlineLevel="1" x14ac:dyDescent="0.3">
@@ -45470,67 +45720,67 @@
       </c>
       <c r="L392" s="15">
         <f>SUMPRODUCT(L393:L406,$J393:$J406)/$J392</f>
-        <v>0.16120492057360689</v>
+        <v>0</v>
       </c>
       <c r="M392" s="15">
         <f t="shared" ref="M392:AC392" si="247">SUMPRODUCT(M393:M406,$J393:$J406)/$J392</f>
-        <v>6.8800314079166411E-2</v>
+        <v>0.23000601071918123</v>
       </c>
       <c r="N392" s="15">
         <f t="shared" si="247"/>
-        <v>6.8800314079166411E-2</v>
+        <v>6.8800702112370368E-2</v>
       </c>
       <c r="O392" s="15">
         <f t="shared" si="247"/>
-        <v>6.8800314079166411E-2</v>
+        <v>6.8800702112370368E-2</v>
       </c>
       <c r="P392" s="15">
         <f t="shared" si="247"/>
-        <v>6.8800314079166411E-2</v>
+        <v>6.8800702112370368E-2</v>
       </c>
       <c r="Q392" s="15">
         <f t="shared" si="247"/>
-        <v>6.8800314079166411E-2</v>
+        <v>6.8800702112370368E-2</v>
       </c>
       <c r="R392" s="15">
         <f t="shared" si="247"/>
-        <v>9.9973826736133795E-3</v>
+        <v>9.9977707068173421E-3</v>
       </c>
       <c r="S392" s="15">
         <f t="shared" si="247"/>
-        <v>6.8800314079166411E-2</v>
+        <v>6.8800702112370368E-2</v>
       </c>
       <c r="T392" s="15">
         <f t="shared" si="247"/>
-        <v>6.8800314079166411E-2</v>
+        <v>6.8800702112370368E-2</v>
       </c>
       <c r="U392" s="15">
         <f t="shared" si="247"/>
-        <v>6.8800314079166411E-2</v>
+        <v>6.8800702112370368E-2</v>
       </c>
       <c r="V392" s="15">
         <f t="shared" si="247"/>
-        <v>9.9973826736133795E-3</v>
+        <v>9.9977707068173421E-3</v>
       </c>
       <c r="W392" s="15">
         <f t="shared" si="247"/>
-        <v>6.8800314079166411E-2</v>
+        <v>6.8800702112370368E-2</v>
       </c>
       <c r="X392" s="15">
         <f t="shared" si="247"/>
-        <v>6.8800314079166411E-2</v>
+        <v>6.8800702112370368E-2</v>
       </c>
       <c r="Y392" s="15">
         <f t="shared" si="247"/>
-        <v>9.9973826736133795E-3</v>
+        <v>9.9977707068173421E-3</v>
       </c>
       <c r="Z392" s="15">
         <f t="shared" si="247"/>
-        <v>9.9973826736133795E-3</v>
+        <v>9.9977707068173421E-3</v>
       </c>
       <c r="AA392" s="15">
         <f t="shared" si="247"/>
-        <v>0.1108024079402757</v>
+        <v>0.11080279597347965</v>
       </c>
       <c r="AB392" s="15">
         <f>SUMPRODUCT(AB393:AB406,$J393:$J406)/$J392</f>
@@ -45544,7 +45794,7 @@
       <c r="AE392" s="15"/>
       <c r="AF392" s="16">
         <f>SUM(L392:AE392)</f>
-        <v>1.0000000000000002</v>
+        <v>1.0000062085312631</v>
       </c>
       <c r="AH392" s="15">
         <f>SUMPRODUCT(AH393:AH406,$J393:$J406)/$J392</f>
@@ -45552,7 +45802,7 @@
       </c>
       <c r="AI392" s="15">
         <f t="shared" ref="AI392:AW392" si="248">SUMPRODUCT(AI393:AI406,$J393:$J406)/$J392</f>
-        <v>0.54119706859444705</v>
+        <v>0.54120079371320517</v>
       </c>
       <c r="AJ392" s="15">
         <f t="shared" si="248"/>
@@ -45588,7 +45838,7 @@
       </c>
       <c r="AR392" s="15">
         <f t="shared" si="248"/>
-        <v>0.28239413718889395</v>
+        <v>0.28239662060139936</v>
       </c>
       <c r="AS392" s="15">
         <f t="shared" si="248"/>
@@ -45628,7 +45878,7 @@
       </c>
       <c r="BB392" s="50">
         <f>SUM(AH392:BA392)</f>
-        <v>1</v>
+        <v>1.0000062085312638</v>
       </c>
     </row>
     <row r="393" spans="2:54" s="29" customFormat="1" ht="13.8" outlineLevel="2" x14ac:dyDescent="0.3">
@@ -45744,10 +45994,10 @@
         <f t="shared" si="250"/>
         <v>31041.004500000003</v>
       </c>
-      <c r="L394" s="27">
-        <v>1</v>
-      </c>
-      <c r="M394" s="27"/>
+      <c r="L394" s="27"/>
+      <c r="M394" s="27">
+        <v>1</v>
+      </c>
       <c r="N394" s="27"/>
       <c r="O394" s="27"/>
       <c r="P394" s="27"/>
@@ -45827,10 +46077,10 @@
         <f t="shared" si="250"/>
         <v>19753.366500000004</v>
       </c>
-      <c r="L395" s="27">
-        <v>1</v>
-      </c>
-      <c r="M395" s="27"/>
+      <c r="L395" s="27"/>
+      <c r="M395" s="27">
+        <v>1</v>
+      </c>
       <c r="N395" s="27"/>
       <c r="O395" s="27"/>
       <c r="P395" s="27"/>
@@ -46729,8 +46979,8 @@
       <c r="G406" s="23">
         <v>48</v>
       </c>
-      <c r="H406" s="25">
-        <v>527.65020833333335</v>
+      <c r="H406" s="71">
+        <v>527.69365833323889</v>
       </c>
       <c r="I406" s="25">
         <f>28406.7/48</f>
@@ -46738,13 +46988,11 @@
       </c>
       <c r="J406" s="25">
         <f t="shared" si="250"/>
-        <v>53733.91</v>
-      </c>
-      <c r="L406" s="53">
-        <v>6.25E-2</v>
-      </c>
+        <v>53735.995599995469</v>
+      </c>
+      <c r="L406" s="53"/>
       <c r="M406" s="53">
-        <v>6.25E-2</v>
+        <v>0.125</v>
       </c>
       <c r="N406" s="53">
         <v>6.25E-2</v>
@@ -47567,18 +47815,9 @@
         <v>1</v>
       </c>
     </row>
-    <row r="411" spans="2:54" hidden="1" x14ac:dyDescent="0.3"/>
-    <row r="412" spans="2:54" hidden="1" x14ac:dyDescent="0.3"/>
-    <row r="413" spans="2:54" hidden="1" x14ac:dyDescent="0.3"/>
   </sheetData>
   <sheetProtection formatCells="0" formatColumns="0" formatRows="0" insertHyperlinks="0" selectLockedCells="1" sort="0" autoFilter="0" pivotTables="0"/>
-  <autoFilter ref="A3:BB413" xr:uid="{21612B2B-65B0-4042-AF89-F6179AF39AA4}">
-    <filterColumn colId="1">
-      <customFilters>
-        <customFilter operator="notEqual" val=" "/>
-      </customFilters>
-    </filterColumn>
-  </autoFilter>
+  <autoFilter ref="A3:BB413" xr:uid="{21612B2B-65B0-4042-AF89-F6179AF39AA4}"/>
   <mergeCells count="14">
     <mergeCell ref="AH2:BB2"/>
     <mergeCell ref="B2:B5"/>
@@ -47597,145 +47836,145 @@
   </mergeCells>
   <phoneticPr fontId="4" type="noConversion"/>
   <conditionalFormatting sqref="L8:AE55 AH8:BA55 L56 N56:S56 U56:AE56 AH56:AN56 AP56:BA56 AH57:BA57 L57:AE60 AJ58:BA60 L61:P61 Q61:Q62 R61:AE64 L62:N62 L63:P65 S65:AE65 L66:AE71 P72:U72 V72:AE81 L72:N82 O73:T76 O77:Q77 O78 O79:Q81 P82:AE82 L83:AE87 AH83:BA87 L88:M88 O88:AE88 L89:S96 U89:AE97 L97:P97 R97:S97 L98:AE103 P104:U104 L104:N113 AE104:AE117 N105:T112 L118:AE152 AH119:BA152 L153:V162 X153:AE162 L163:AE222 AH163:BA222 L223:N229 L230:M236 L237:AE283 AH237:BA283 L284:O285 R284:AE285 L286:AE287 L288:P288 S288:AE289 L289:Q289 L290:AE330 AH290:BA330 L331:M339 U331:AE339 L340:AE346 V347:AE355 R356:AE356 R357:AD359 L360:AE372 AH360:BA410 AE373 L373:AC375 L376:AE410">
-    <cfRule type="cellIs" dxfId="23" priority="49" operator="between">
+    <cfRule type="cellIs" dxfId="56" priority="49" operator="between">
       <formula>0.0000000001</formula>
       <formula>1</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="N113:Q113 S113:T113">
-    <cfRule type="cellIs" dxfId="22" priority="39" operator="between">
+    <cfRule type="cellIs" dxfId="55" priority="39" operator="between">
       <formula>0.0000000001</formula>
       <formula>1</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="N331:T338 N339:Q339 S339:T339">
-    <cfRule type="cellIs" dxfId="21" priority="36" operator="between">
+    <cfRule type="cellIs" dxfId="54" priority="36" operator="between">
       <formula>0.0000000001</formula>
       <formula>1</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="N232:V232">
-    <cfRule type="cellIs" dxfId="20" priority="43" operator="between">
+    <cfRule type="cellIs" dxfId="53" priority="43" operator="between">
       <formula>0.0000000001</formula>
       <formula>1</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="O355:R355 T355:U355">
-    <cfRule type="cellIs" dxfId="19" priority="34" operator="between">
+    <cfRule type="cellIs" dxfId="52" priority="34" operator="between">
       <formula>0.0000000001</formula>
       <formula>1</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="O223:U231">
-    <cfRule type="cellIs" dxfId="18" priority="37" operator="between">
+    <cfRule type="cellIs" dxfId="51" priority="37" operator="between">
       <formula>0.0000000001</formula>
       <formula>1</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="P347:U354 L347:O359">
-    <cfRule type="cellIs" dxfId="17" priority="35" operator="between">
+    <cfRule type="cellIs" dxfId="50" priority="35" operator="between">
       <formula>0.0000000001</formula>
       <formula>1</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="R77:R78 S77:T80 T81">
-    <cfRule type="cellIs" dxfId="16" priority="40" operator="between">
+    <cfRule type="cellIs" dxfId="49" priority="40" operator="between">
       <formula>0.0000000001</formula>
       <formula>1</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="V231">
-    <cfRule type="cellIs" dxfId="15" priority="44" operator="between">
+    <cfRule type="cellIs" dxfId="48" priority="44" operator="between">
       <formula>0.0000000001</formula>
       <formula>1</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="V223:AE230 N230:N231 W231:AE232 N233:AE236">
-    <cfRule type="cellIs" dxfId="14" priority="46" operator="between">
+    <cfRule type="cellIs" dxfId="47" priority="46" operator="between">
       <formula>0.0000000001</formula>
       <formula>1</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="W104:AD113 L114:AD117">
-    <cfRule type="cellIs" dxfId="13" priority="42" operator="between">
+    <cfRule type="cellIs" dxfId="46" priority="42" operator="between">
       <formula>0.0000000001</formula>
       <formula>1</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="AH58:AI65 AJ61:AL61 AM61:AM62 AN61:BA64 AJ62 AJ63:AL65 AO65:BA65 AH66:BA71 AR72:BA81 AH72:AJ82 AK82:BA82 AH88:AI88 AK88:BA88 AH89:AO89 AQ89:BA97 AJ90:AO96 AH90:AI97 AJ97:AL97 AN97:AO97 AH98:BA103 AL104:AQ104 AH104:AJ113 AK105:AP112 AH114:AL117 AH118:AV118 AH153:AR162 AT153:BA162 AH223:AJ223 AJ224:AJ232 AH224:AI236 AH284:AK285 AN284:BA285 AH286:BA287 AH288:AL288 AO288:BA289 AH289:AM289 AH331:AI339 AQ331:BA339 AH340:BA346 AR347:BA355 AM356:BA356 AN357:BA359">
-    <cfRule type="cellIs" dxfId="12" priority="17" operator="between">
+    <cfRule type="cellIs" dxfId="45" priority="17" operator="between">
       <formula>0.0000000001</formula>
       <formula>1</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="AJ113:AM113 AO113:AP113">
-    <cfRule type="cellIs" dxfId="11" priority="9" operator="between">
+    <cfRule type="cellIs" dxfId="44" priority="9" operator="between">
       <formula>0.0000000001</formula>
       <formula>1</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="AJ331:AP338 AJ339:AM339 AO339:AP339">
-    <cfRule type="cellIs" dxfId="10" priority="6" operator="between">
+    <cfRule type="cellIs" dxfId="43" priority="6" operator="between">
       <formula>0.0000000001</formula>
       <formula>1</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="AK355:AN355 AP355:AQ355">
-    <cfRule type="cellIs" dxfId="9" priority="4" operator="between">
+    <cfRule type="cellIs" dxfId="42" priority="4" operator="between">
       <formula>0.0000000001</formula>
       <formula>1</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="AK72:AQ76 AK77:AN77 AO77:AO78 AP77:AQ80 AK78:AL78 AK79:AN81 AQ81">
-    <cfRule type="cellIs" dxfId="8" priority="10" operator="between">
+    <cfRule type="cellIs" dxfId="41" priority="10" operator="between">
       <formula>0.0000000001</formula>
       <formula>1</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="AK223:AQ231">
-    <cfRule type="cellIs" dxfId="7" priority="7" operator="between">
+    <cfRule type="cellIs" dxfId="40" priority="7" operator="between">
       <formula>0.0000000001</formula>
       <formula>1</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="AK232:AR232">
-    <cfRule type="cellIs" dxfId="6" priority="12" operator="between">
+    <cfRule type="cellIs" dxfId="39" priority="12" operator="between">
       <formula>0.0000000001</formula>
       <formula>1</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="AL347:AQ354 AH347:AK359">
-    <cfRule type="cellIs" dxfId="5" priority="5" operator="between">
+    <cfRule type="cellIs" dxfId="38" priority="5" operator="between">
       <formula>0.0000000001</formula>
       <formula>1</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="AR231">
-    <cfRule type="cellIs" dxfId="4" priority="13" operator="between">
+    <cfRule type="cellIs" dxfId="37" priority="13" operator="between">
       <formula>0.0000000001</formula>
       <formula>1</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="AR223:BA230 AS231:BA232 AJ233:BA236">
-    <cfRule type="cellIs" dxfId="3" priority="15" operator="between">
+    <cfRule type="cellIs" dxfId="36" priority="15" operator="between">
       <formula>0.0000000001</formula>
       <formula>1</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="AS104:BA113 AM114:BA115 AM116:AV117 AW116:BA118">
-    <cfRule type="cellIs" dxfId="2" priority="11" operator="between">
+    <cfRule type="cellIs" dxfId="35" priority="11" operator="between">
       <formula>0.0000000001</formula>
       <formula>1</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="BB4 AF4:AF410">
-    <cfRule type="cellIs" dxfId="1" priority="53" operator="notBetween">
+    <cfRule type="cellIs" dxfId="34" priority="53" operator="notBetween">
       <formula>0</formula>
       <formula>1</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="BB6:BB410">
-    <cfRule type="cellIs" dxfId="0" priority="18" operator="notBetween">
+    <cfRule type="cellIs" dxfId="33" priority="18" operator="notBetween">
       <formula>0</formula>
       <formula>1</formula>
     </cfRule>
